--- a/用卷/1988.xlsx
+++ b/用卷/1988.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AAB828-356C-4331-B997-82F56858DB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8388E7-99E1-45FA-8AF3-9BED5C6195CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,10 +206,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>英语为MET,政治为北京卷,其他科目为全国卷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>天津政治实验点</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -258,11 +254,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>全国卷,北京卷,天津卷,吉林卷,上海实验卷,上海卷,广东卷,贵州卷</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>分科卷数统计</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语为MET,政治为北师大卷,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国卷,北师大卷,天津卷,吉林卷,上海实验卷,上海卷,广东卷,贵州卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -444,10 +444,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -735,11 +735,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -776,7 +776,7 @@
         <v>52</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D4" s="21"/>
     </row>
@@ -797,7 +797,7 @@
         <v>1988</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>53</v>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="8"/>
     </row>
@@ -848,7 +848,7 @@
         <v>43</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="9"/>
     </row>
@@ -869,10 +869,10 @@
         <v>1988</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="18"/>
     </row>
@@ -884,7 +884,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="9"/>
     </row>
@@ -896,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="10"/>
     </row>
@@ -905,10 +905,10 @@
         <v>1988</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="18"/>
     </row>
@@ -968,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="9"/>
     </row>
@@ -980,7 +980,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="9"/>
     </row>
@@ -992,7 +992,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="9"/>
     </row>
@@ -1004,7 +1004,7 @@
         <v>12</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="9"/>
     </row>
@@ -1028,7 +1028,7 @@
         <v>14</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D25" s="17"/>
     </row>
@@ -1073,10 +1073,10 @@
         <v>1988</v>
       </c>
       <c r="B29" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>61</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>62</v>
       </c>
       <c r="D29" s="11"/>
     </row>
@@ -1088,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="13"/>
     </row>
@@ -1112,7 +1112,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="11"/>
     </row>
@@ -1136,7 +1136,7 @@
         <v>41</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D34" s="9"/>
     </row>
@@ -1148,7 +1148,7 @@
         <v>22</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="8"/>
     </row>
@@ -1160,7 +1160,7 @@
         <v>23</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" s="11"/>
     </row>
@@ -1172,7 +1172,7 @@
         <v>24</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37" s="9"/>
     </row>
@@ -1183,11 +1183,11 @@
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
+      <c r="A39" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
       <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -1234,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D43" s="7"/>
     </row>
@@ -1258,7 +1258,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D45" s="19"/>
     </row>
@@ -1294,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D48" s="7"/>
     </row>
